--- a/ITU/course.xlsx
+++ b/ITU/course.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ADBE5D-BB9D-4BF6-B699-D780A3A76564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB25534-C69D-4BFB-85F9-F70247BE48DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Link" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Faculty of Electrical and Electronics Engineering</t>
   </si>
@@ -86,12 +87,24 @@
   <si>
     <t>https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/course-plans.php?fakulte=IS</t>
   </si>
+  <si>
+    <t>https://www.sis.itu.edu.tr/onkayitlar/lsyabanci/basvuru/index.php?islem=kontenjanlar-sartlar</t>
+  </si>
+  <si>
+    <t>Quotas, Requirements and Descriptions</t>
+  </si>
+  <si>
+    <t>undergraduate programs of ITU</t>
+  </si>
+  <si>
+    <t>https://www.itu.edu.tr/en/all-departments</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +141,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -215,7 +234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -230,9 +249,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -514,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.42578125" customWidth="1"/>
@@ -582,7 +600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="8" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="6" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>0</v>
       </c>
@@ -593,26 +611,56 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D281B26-88D0-4B07-911B-4BC1C12CD033}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="90.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" xr:uid="{5656C5A9-D6A8-4A1D-9E8A-CCDCF8192914}"/>
-    <hyperlink ref="B13" r:id="rId2" xr:uid="{8EAAD1B9-EF9B-4720-BD4B-867AAB868575}"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{5656C5A9-D6A8-4A1D-9E8A-CCDCF8192914}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{8EAAD1B9-EF9B-4720-BD4B-867AAB868575}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
